--- a/Project 1 Data Quality Assessment/D4 Parallel-redundancy Temporal Consistency/outputs/figure_source_data/FigD4_2_pair_mechanism_profile_source_data.xlsx
+++ b/Project 1 Data Quality Assessment/D4 Parallel-redundancy Temporal Consistency/outputs/figure_source_data/FigD4_2_pair_mechanism_profile_source_data.xlsx
@@ -482,7 +482,7 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>3.731613335567097</v>
+        <v>3.818166776968895</v>
       </c>
       <c r="E2" t="n">
         <v>4</v>
@@ -491,7 +491,7 @@
         <v>4</v>
       </c>
       <c r="G2" t="n">
-        <v>5969</v>
+        <v>6044</v>
       </c>
     </row>
     <row r="3">
@@ -509,7 +509,7 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>4.050427207237393</v>
+        <v>4.068001323626738</v>
       </c>
       <c r="E3" t="n">
         <v>4</v>
@@ -518,7 +518,7 @@
         <v>5</v>
       </c>
       <c r="G3" t="n">
-        <v>5969</v>
+        <v>6044</v>
       </c>
     </row>
     <row r="4">
@@ -536,7 +536,7 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>4.152286815211928</v>
+        <v>4.120946393117141</v>
       </c>
       <c r="E4" t="n">
         <v>4</v>
@@ -545,7 +545,7 @@
         <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>5969</v>
+        <v>6044</v>
       </c>
     </row>
     <row r="5">
@@ -563,7 +563,7 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>2.787736639303066</v>
+        <v>2.78590337524818</v>
       </c>
       <c r="E5" t="n">
         <v>2</v>
@@ -572,7 +572,7 @@
         <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>5969</v>
+        <v>6044</v>
       </c>
     </row>
     <row r="6">
@@ -590,7 +590,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>4.133355393778954</v>
+        <v>4.221009098428453</v>
       </c>
       <c r="E6" t="n">
         <v>4</v>
@@ -599,7 +599,7 @@
         <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>6044</v>
+        <v>6045</v>
       </c>
     </row>
     <row r="7">
@@ -617,7 +617,7 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>4.033421575115818</v>
+        <v>4.054755996691481</v>
       </c>
       <c r="E7" t="n">
         <v>4</v>
@@ -626,7 +626,7 @@
         <v>5</v>
       </c>
       <c r="G7" t="n">
-        <v>6044</v>
+        <v>6045</v>
       </c>
     </row>
     <row r="8">
@@ -644,16 +644,16 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>3.981800132362674</v>
+        <v>3.954011579818031</v>
       </c>
       <c r="E8" t="n">
         <v>4</v>
       </c>
       <c r="F8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G8" t="n">
-        <v>6044</v>
+        <v>6045</v>
       </c>
     </row>
     <row r="9">
@@ -671,7 +671,7 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>2.626902713434812</v>
+        <v>2.627295285359801</v>
       </c>
       <c r="E9" t="n">
         <v>2</v>
@@ -680,7 +680,7 @@
         <v>3</v>
       </c>
       <c r="G9" t="n">
-        <v>6044</v>
+        <v>6045</v>
       </c>
     </row>
     <row r="10">
@@ -698,7 +698,7 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>3.87394540942928</v>
+        <v>4.003639371381307</v>
       </c>
       <c r="E10" t="n">
         <v>4</v>
@@ -725,7 +725,7 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>3.824317617866005</v>
+        <v>3.858726220016543</v>
       </c>
       <c r="E11" t="n">
         <v>4</v>
@@ -752,7 +752,7 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>3.572043010752688</v>
+        <v>3.599503722084367</v>
       </c>
       <c r="E12" t="n">
         <v>3</v>
@@ -806,7 +806,7 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>2.911166253101737</v>
+        <v>3.037220843672456</v>
       </c>
       <c r="E14" t="n">
         <v>3</v>
@@ -833,7 +833,7 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>4.212241521918942</v>
+        <v>4.217866004962779</v>
       </c>
       <c r="E15" t="n">
         <v>5</v>
@@ -860,7 +860,7 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>4.031430934656741</v>
+        <v>4.037220843672457</v>
       </c>
       <c r="E16" t="n">
         <v>5</v>
@@ -914,7 +914,7 @@
         <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>3.836991150442478</v>
+        <v>3.925296833773087</v>
       </c>
       <c r="E18" t="n">
         <v>4</v>
@@ -923,7 +923,7 @@
         <v>4</v>
       </c>
       <c r="G18" t="n">
-        <v>5650</v>
+        <v>6064</v>
       </c>
     </row>
     <row r="19">
@@ -941,7 +941,7 @@
         <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>4.058407079646018</v>
+        <v>4.113621372031663</v>
       </c>
       <c r="E19" t="n">
         <v>4</v>
@@ -950,7 +950,7 @@
         <v>5</v>
       </c>
       <c r="G19" t="n">
-        <v>5650</v>
+        <v>6064</v>
       </c>
     </row>
     <row r="20">
@@ -968,7 +968,7 @@
         <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>3.94141592920354</v>
+        <v>3.95976253298153</v>
       </c>
       <c r="E20" t="n">
         <v>4</v>
@@ -977,7 +977,7 @@
         <v>5</v>
       </c>
       <c r="G20" t="n">
-        <v>5650</v>
+        <v>6064</v>
       </c>
     </row>
     <row r="21">
@@ -995,7 +995,7 @@
         <v>3</v>
       </c>
       <c r="D21" t="n">
-        <v>3.135929203539823</v>
+        <v>3.147757255936675</v>
       </c>
       <c r="E21" t="n">
         <v>3</v>
@@ -1004,7 +1004,7 @@
         <v>3</v>
       </c>
       <c r="G21" t="n">
-        <v>5650</v>
+        <v>6064</v>
       </c>
     </row>
     <row r="22">
@@ -1022,16 +1022,16 @@
         <v>3</v>
       </c>
       <c r="D22" t="n">
-        <v>3.125493841505926</v>
+        <v>3.067282321899736</v>
       </c>
       <c r="E22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G22" t="n">
-        <v>4303</v>
+        <v>6064</v>
       </c>
     </row>
     <row r="23">
@@ -1049,7 +1049,7 @@
         <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>3.853358122240298</v>
+        <v>3.888027704485488</v>
       </c>
       <c r="E23" t="n">
         <v>4</v>
@@ -1058,7 +1058,7 @@
         <v>4</v>
       </c>
       <c r="G23" t="n">
-        <v>4303</v>
+        <v>6064</v>
       </c>
     </row>
     <row r="24">
@@ -1076,16 +1076,16 @@
         <v>3</v>
       </c>
       <c r="D24" t="n">
-        <v>2.948872879386474</v>
+        <v>2.70646437994723</v>
       </c>
       <c r="E24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G24" t="n">
-        <v>4303</v>
+        <v>6064</v>
       </c>
     </row>
     <row r="25">
@@ -1103,7 +1103,7 @@
         <v>3</v>
       </c>
       <c r="D25" t="n">
-        <v>3.530792470369509</v>
+        <v>3.531827176781003</v>
       </c>
       <c r="E25" t="n">
         <v>3</v>
@@ -1112,7 +1112,7 @@
         <v>4</v>
       </c>
       <c r="G25" t="n">
-        <v>4303</v>
+        <v>6064</v>
       </c>
     </row>
     <row r="26">
@@ -1130,7 +1130,7 @@
         <v>3</v>
       </c>
       <c r="D26" t="n">
-        <v>2.923174764690919</v>
+        <v>2.924142480211082</v>
       </c>
       <c r="E26" t="n">
         <v>2</v>
@@ -1139,7 +1139,7 @@
         <v>3</v>
       </c>
       <c r="G26" t="n">
-        <v>3931</v>
+        <v>6064</v>
       </c>
     </row>
     <row r="27">
@@ -1157,7 +1157,7 @@
         <v>3</v>
       </c>
       <c r="D27" t="n">
-        <v>3.203256168913762</v>
+        <v>3.298977572559367</v>
       </c>
       <c r="E27" t="n">
         <v>3</v>
@@ -1166,7 +1166,7 @@
         <v>4</v>
       </c>
       <c r="G27" t="n">
-        <v>3931</v>
+        <v>6064</v>
       </c>
     </row>
     <row r="28">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D28" t="n">
-        <v>2.843042482828797</v>
+        <v>2.546503957783641</v>
       </c>
       <c r="E28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
         <v>3</v>
       </c>
       <c r="G28" t="n">
-        <v>3931</v>
+        <v>6064</v>
       </c>
     </row>
     <row r="29">
@@ -1211,7 +1211,7 @@
         <v>3</v>
       </c>
       <c r="D29" t="n">
-        <v>2.996438565250573</v>
+        <v>2.844986807387863</v>
       </c>
       <c r="E29" t="n">
         <v>2</v>
@@ -1220,7 +1220,7 @@
         <v>3</v>
       </c>
       <c r="G29" t="n">
-        <v>3931</v>
+        <v>6064</v>
       </c>
     </row>
   </sheetData>
@@ -1281,7 +1281,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.367710252973697</v>
+        <v>3.394775810721376</v>
       </c>
       <c r="C2" t="n">
         <v>3.4</v>
@@ -1293,10 +1293,10 @@
         <v>4.6</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3141229686714693</v>
+        <v>0.2908669755129054</v>
       </c>
       <c r="G2" t="n">
-        <v>5969</v>
+        <v>6044</v>
       </c>
     </row>
     <row r="3">
@@ -1306,22 +1306,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.391024156187955</v>
+        <v>3.421027708850289</v>
       </c>
       <c r="C3" t="n">
         <v>3.4</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0125</v>
+        <v>2.125</v>
       </c>
       <c r="E3" t="n">
         <v>4.6</v>
       </c>
       <c r="F3" t="n">
-        <v>0.264559894109861</v>
+        <v>0.2489660876757651</v>
       </c>
       <c r="G3" t="n">
-        <v>6044</v>
+        <v>6045</v>
       </c>
     </row>
     <row r="4">
@@ -1331,19 +1331,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.19844499586435</v>
+        <v>3.258610421836228</v>
       </c>
       <c r="C4" t="n">
-        <v>3.2125</v>
+        <v>3.25</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8625</v>
+        <v>2.05</v>
       </c>
       <c r="E4" t="n">
         <v>4.5625</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4059553349875931</v>
+        <v>0.3655913978494624</v>
       </c>
       <c r="G4" t="n">
         <v>6045</v>
@@ -1356,19 +1356,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.977698511166253</v>
+        <v>3.022140198511166</v>
       </c>
       <c r="C5" t="n">
-        <v>3.05</v>
+        <v>3.1375</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5325</v>
+        <v>1.5625</v>
       </c>
       <c r="E5" t="n">
         <v>4.337499999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4775847808105873</v>
+        <v>0.4574028122415219</v>
       </c>
       <c r="G5" t="n">
         <v>6045</v>
@@ -1381,22 +1381,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.425426991150442</v>
+        <v>3.481237631926121</v>
       </c>
       <c r="C6" t="n">
-        <v>3.425</v>
+        <v>3.4875</v>
       </c>
       <c r="D6" t="n">
-        <v>2.05</v>
+        <v>2.1625</v>
       </c>
       <c r="E6" t="n">
         <v>4.6</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2766371681415929</v>
+        <v>0.2521437994722955</v>
       </c>
       <c r="G6" t="n">
-        <v>5650</v>
+        <v>6064</v>
       </c>
     </row>
     <row r="7">
@@ -1406,22 +1406,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.04028584708343</v>
+        <v>2.971229798812665</v>
       </c>
       <c r="C7" t="n">
-        <v>3.0125</v>
+        <v>2.875</v>
       </c>
       <c r="D7" t="n">
-        <v>1.675</v>
+        <v>1.75</v>
       </c>
       <c r="E7" t="n">
-        <v>4.4125</v>
+        <v>4.3375</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4924471299093656</v>
+        <v>0.5371042216358839</v>
       </c>
       <c r="G7" t="n">
-        <v>4303</v>
+        <v>6064</v>
       </c>
     </row>
     <row r="8">
@@ -1431,22 +1431,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.649996820147545</v>
+        <v>2.588710009894459</v>
       </c>
       <c r="C8" t="n">
-        <v>2.5625</v>
+        <v>2.5</v>
       </c>
       <c r="D8" t="n">
         <v>1.45</v>
       </c>
       <c r="E8" t="n">
-        <v>4.050000000000001</v>
+        <v>3.975</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6761638259984737</v>
+        <v>0.7074538258575198</v>
       </c>
       <c r="G8" t="n">
-        <v>3931</v>
+        <v>6064</v>
       </c>
     </row>
   </sheetData>
@@ -1505,10 +1505,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>2316</v>
+        <v>569</v>
       </c>
       <c r="D2" t="n">
-        <v>2316</v>
+        <v>569</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1531,10 +1531,10 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>746</v>
+        <v>732</v>
       </c>
       <c r="D3" t="n">
-        <v>746</v>
+        <v>732</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -1557,10 +1557,10 @@
         <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>1060</v>
+        <v>1106</v>
       </c>
       <c r="D4" t="n">
-        <v>1060</v>
+        <v>1106</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1609,10 +1609,10 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>312</v>
+        <v>465</v>
       </c>
       <c r="D6" t="n">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1635,10 +1635,10 @@
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>312</v>
+        <v>465</v>
       </c>
       <c r="D7" t="n">
-        <v>32</v>
+        <v>97</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1661,10 +1661,10 @@
         <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>145</v>
+        <v>247</v>
       </c>
       <c r="D8" t="n">
-        <v>145</v>
+        <v>247</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1687,10 +1687,10 @@
         <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>312</v>
+        <v>465</v>
       </c>
       <c r="D9" t="n">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>

--- a/Project 1 Data Quality Assessment/D4 Parallel-redundancy Temporal Consistency/outputs/figure_source_data/FigD4_2_pair_mechanism_profile_source_data.xlsx
+++ b/Project 1 Data Quality Assessment/D4 Parallel-redundancy Temporal Consistency/outputs/figure_source_data/FigD4_2_pair_mechanism_profile_source_data.xlsx
@@ -1460,7 +1460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1494,6 +1494,16 @@
           <t>calibration_quality</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>exact_independent_blocks</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>percentile_precision_grade</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1520,6 +1530,14 @@
           <t>adequate</t>
         </is>
       </c>
+      <c r="G2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>wide_interval</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1546,6 +1564,14 @@
           <t>adequate</t>
         </is>
       </c>
+      <c r="G3" t="n">
+        <v>12</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1572,6 +1598,14 @@
           <t>adequate</t>
         </is>
       </c>
+      <c r="G4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1598,6 +1632,14 @@
           <t>adequate</t>
         </is>
       </c>
+      <c r="G5" t="n">
+        <v>7</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1624,6 +1666,14 @@
           <t>limited_regime_support</t>
         </is>
       </c>
+      <c r="G6" t="n">
+        <v>4</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1650,6 +1700,14 @@
           <t>limited_regime_support</t>
         </is>
       </c>
+      <c r="G7" t="n">
+        <v>10</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1676,6 +1734,14 @@
           <t>adequate</t>
         </is>
       </c>
+      <c r="G8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1700,6 +1766,14 @@
       <c r="F9" t="inlineStr">
         <is>
           <t>limited_regime_support</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>6</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>supported</t>
         </is>
       </c>
     </row>
